--- a/data/trans_camb/P13_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P13_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,16</t>
+          <t>1,21; 5,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,8</t>
+          <t>0,26; 4,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,66</t>
+          <t>2,49; 6,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,91</t>
+          <t>6,36; 11,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 7,01</t>
+          <t>2,44; 6,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,89</t>
+          <t>3,38; 6,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,8</t>
+          <t>4,48; 7,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,72</t>
+          <t>1,92; 4,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,04</t>
+          <t>3,44; 6,15</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>44,93; 410,69</t>
+          <t>38,88; 466,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,04; 306,05</t>
+          <t>7,03; 382,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95,49; 543,79</t>
+          <t>80,49; 576,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>209,07; 863,79</t>
+          <t>213,56; 884,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>71,75; 523,42</t>
+          <t>79,99; 518,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>102,14; 521,73</t>
+          <t>105,29; 572,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>170,08; 570,86</t>
+          <t>184,85; 565,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>69,88; 339,33</t>
+          <t>77,58; 339,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>128,94; 433,07</t>
+          <t>132,64; 421,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,98</t>
+          <t>-1,18; 2,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,26</t>
+          <t>-3,31; 0,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,87</t>
+          <t>-3,47; 0,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,0</t>
+          <t>1,61; 6,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,2</t>
+          <t>-1,8; 2,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,82</t>
+          <t>1,18; 4,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,91</t>
+          <t>0,85; 3,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,75</t>
+          <t>-1,91; 0,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,1</t>
+          <t>-1,23; 2,16</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,89; 98,3</t>
+          <t>-24,11; 86,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,7; 12,48</t>
+          <t>-61,95; 8,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,34; 27,67</t>
+          <t>-63,88; 23,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,83; 186,52</t>
+          <t>27,42; 179,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,2; 67,17</t>
+          <t>-34,9; 64,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,48; 152,04</t>
+          <t>20,09; 149,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 113,16</t>
+          <t>16,59; 103,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 23,01</t>
+          <t>-38,69; 17,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,4; 56,83</t>
+          <t>-24,55; 60,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,99</t>
+          <t>-1,43; 2,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 2,29</t>
+          <t>-1,78; 2,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 4,16</t>
+          <t>-0,28; 4,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,05</t>
+          <t>0,42; 6,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,12</t>
+          <t>-2,73; 2,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 2,33</t>
+          <t>-3,6; 2,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,65</t>
+          <t>0,23; 3,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,53</t>
+          <t>-1,6; 1,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,39</t>
+          <t>-1,49; 2,45</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-36,94; 138,13</t>
+          <t>-32,3; 124,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 105,05</t>
+          <t>-40,38; 98,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 192,2</t>
+          <t>-13,34; 164,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,09; 142,22</t>
+          <t>5,86; 139,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,23; 50,64</t>
+          <t>-41,73; 49,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,66; 52,28</t>
+          <t>-52,49; 47,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 101,25</t>
+          <t>4,23; 106,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,89; 44,47</t>
+          <t>-32,0; 40,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 63,63</t>
+          <t>-28,03; 66,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,29</t>
+          <t>-0,39; 3,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,38</t>
+          <t>-1,21; 2,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,65</t>
+          <t>0,93; 4,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,55</t>
+          <t>0,78; 5,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,81</t>
+          <t>-2,76; 1,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,1</t>
+          <t>-1,37; 3,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,84</t>
+          <t>0,97; 3,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,46</t>
+          <t>-1,34; 1,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,4</t>
+          <t>0,38; 3,3</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 137,69</t>
+          <t>-10,51; 130,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 92,53</t>
+          <t>-29,15; 87,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,48; 189,68</t>
+          <t>19,99; 193,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,07; 97,92</t>
+          <t>8,8; 98,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 33,77</t>
+          <t>-34,2; 28,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 53,35</t>
+          <t>-17,8; 52,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,39; 89,57</t>
+          <t>15,98; 94,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 34,03</t>
+          <t>-23,27; 34,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,59; 75,93</t>
+          <t>5,94; 73,58</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,49</t>
+          <t>0,36; 2,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,08</t>
+          <t>-0,66; 1,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,75</t>
+          <t>0,48; 2,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,74</t>
+          <t>3,3; 5,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,79</t>
+          <t>-0,33; 1,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,05</t>
+          <t>0,52; 3,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,72</t>
+          <t>2,28; 3,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,19</t>
+          <t>-0,23; 1,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,58</t>
+          <t>0,89; 2,6</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>12,65; 87,05</t>
+          <t>9,0; 89,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 37,89</t>
+          <t>-18,14; 44,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12,19; 101,55</t>
+          <t>13,83; 94,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59,61; 133,82</t>
+          <t>60,4; 133,07</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 41,35</t>
+          <t>-5,9; 42,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,59; 70,61</t>
+          <t>9,97; 74,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,49; 99,88</t>
+          <t>51,46; 102,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 31,99</t>
+          <t>-5,34; 34,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21,51; 71,03</t>
+          <t>21,36; 70,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P13_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P13_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>4,9</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>4,59</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,28</t>
+          <t>1,3; 5,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,09</t>
+          <t>0,38; 3,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,91</t>
+          <t>2,39; 6,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 11,84</t>
+          <t>6,6; 11,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,67</t>
+          <t>2,32; 6,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,67</t>
+          <t>3,09; 6,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,87</t>
+          <t>4,38; 7,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,77</t>
+          <t>1,77; 4,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,15</t>
+          <t>3,31; 5,94</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>243,23%</t>
+          <t>234,92%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>248,97%</t>
+          <t>246,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>246,87%</t>
+          <t>241,81%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,88; 466,22</t>
+          <t>44,57; 424,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 382,56</t>
+          <t>12,27; 317,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,49; 576,49</t>
+          <t>86,56; 534,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>213,56; 884,85</t>
+          <t>218,95; 940,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>79,99; 518,56</t>
+          <t>76,61; 537,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>105,29; 572,36</t>
+          <t>98,31; 525,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>184,85; 565,32</t>
+          <t>166,89; 537,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>77,58; 339,46</t>
+          <t>67,54; 330,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>132,64; 421,5</t>
+          <t>122,82; 423,65</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,93</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>1,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,74</t>
+          <t>-1,39; 2,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,19</t>
+          <t>-2,96; 0,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,77</t>
+          <t>-1,99; 1,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,17</t>
+          <t>1,56; 6,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,08</t>
+          <t>-1,83; 1,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,98</t>
+          <t>0,92; 4,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,77</t>
+          <t>0,79; 3,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,62</t>
+          <t>-1,91; 0,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,16</t>
+          <t>-0,02; 2,5</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-23,55%</t>
+          <t>-8,55%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 86,89</t>
+          <t>-27,24; 83,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,95; 8,79</t>
+          <t>-59,52; 16,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,88; 23,2</t>
+          <t>-39,74; 49,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,42; 179,8</t>
+          <t>26,73; 189,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 64,42</t>
+          <t>-34,2; 61,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,09; 149,1</t>
+          <t>15,54; 147,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,59; 103,8</t>
+          <t>15,24; 104,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,69; 17,32</t>
+          <t>-40,09; 18,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 60,29</t>
+          <t>-1,23; 71,7</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>1,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,8</t>
+          <t>-1,65; 2,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,28</t>
+          <t>-1,96; 2,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,26</t>
+          <t>0,44; 5,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 6,0</t>
+          <t>0,61; 5,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 2,0</t>
+          <t>-2,63; 2,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 2,3</t>
+          <t>-0,96; 3,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,71</t>
+          <t>0,06; 3,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,47</t>
+          <t>-1,44; 1,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,45</t>
+          <t>0,48; 3,82</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-4,92%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,3; 124,32</t>
+          <t>-39,49; 122,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,38; 98,08</t>
+          <t>-42,91; 95,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 164,16</t>
+          <t>4,58; 231,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,86; 139,99</t>
+          <t>6,86; 130,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 49,12</t>
+          <t>-41,12; 54,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,49; 47,0</t>
+          <t>-14,67; 83,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,23; 106,36</t>
+          <t>0,6; 99,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 40,5</t>
+          <t>-27,52; 43,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,03; 66,15</t>
+          <t>7,7; 104,23</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,22</t>
+          <t>-0,52; 3,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,2</t>
+          <t>-0,85; 2,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,64</t>
+          <t>0,81; 4,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,7</t>
+          <t>0,53; 5,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,66</t>
+          <t>-2,8; 1,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,0</t>
+          <t>-0,65; 3,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,96</t>
+          <t>0,73; 3,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,53</t>
+          <t>-1,37; 1,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,3</t>
+          <t>0,72; 3,45</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 130,65</t>
+          <t>-13,65; 131,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 87,18</t>
+          <t>-21,74; 103,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,99; 193,0</t>
+          <t>18,16; 177,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,8; 98,56</t>
+          <t>6,82; 91,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,2; 28,86</t>
+          <t>-35,11; 31,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 52,84</t>
+          <t>-7,92; 67,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,98; 94,01</t>
+          <t>12,59; 86,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 34,27</t>
+          <t>-23,83; 35,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,94; 73,58</t>
+          <t>11,23; 77,99</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>2,34</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,5</t>
+          <t>0,6; 2,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,21</t>
+          <t>-0,61; 1,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,69</t>
+          <t>1,09; 3,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,8</t>
+          <t>3,3; 5,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,81</t>
+          <t>-0,52; 1,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,21</t>
+          <t>1,58; 3,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,8</t>
+          <t>2,16; 3,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,27</t>
+          <t>-0,18; 1,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,6</t>
+          <t>1,66; 3,02</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,0; 89,38</t>
+          <t>15,65; 97,16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 44,29</t>
+          <t>-17,34; 40,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13,83; 94,27</t>
+          <t>29,4; 112,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60,4; 133,07</t>
+          <t>60,87; 133,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 42,1</t>
+          <t>-9,66; 39,7</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,97; 74,16</t>
+          <t>28,17; 87,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,46; 102,31</t>
+          <t>50,02; 104,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 34,72</t>
+          <t>-4,3; 33,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21,36; 70,38</t>
+          <t>38,17; 83,38</t>
         </is>
       </c>
     </row>
